--- a/artfynd/A 37238-2026 artfynd.xlsx
+++ b/artfynd/A 37238-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136125287</v>
       </c>
       <c r="B2" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136109745</v>
       </c>
       <c r="B3" t="n">
-        <v>99321</v>
+        <v>99324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37238-2026 artfynd.xlsx
+++ b/artfynd/A 37238-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136125287</v>
       </c>
       <c r="B2" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136109745</v>
       </c>
       <c r="B3" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37238-2026 artfynd.xlsx
+++ b/artfynd/A 37238-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136125287</v>
       </c>
       <c r="B2" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>136109745</v>
       </c>
       <c r="B3" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
